--- a/Время.xlsx
+++ b/Время.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arkebuzz\Documents\Converter\Converter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:0_{496C0725-D30C-4A0D-8715-2459CAC1923E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77C4AB7-204F-4E12-A954-2F1236BEBCBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13968" xr2:uid="{3221C338-80F3-471B-93E0-C0262F9A8AF2}"/>
   </bookViews>
@@ -98,7 +98,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -151,13 +151,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -472,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FB46B0-FE15-4D23-B737-CACA5C5BE9C3}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -490,10 +491,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8"/>
+      <c r="B3" s="9"/>
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
@@ -502,11 +503,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10">
+      <c r="B4" s="10"/>
+      <c r="C4" s="8">
         <v>3000</v>
       </c>
       <c r="D4" s="1">
@@ -515,11 +516,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10">
+      <c r="B5" s="10"/>
+      <c r="C5" s="8">
         <f>1/D5</f>
         <v>1220.703125</v>
       </c>
@@ -529,11 +530,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10">
+      <c r="B6" s="10"/>
+      <c r="C6" s="8">
         <f>1/D6</f>
         <v>2857.1428571428573</v>
       </c>
@@ -638,6 +639,13 @@
         <f>600*10^-9</f>
         <v>6.0000000000000008E-7</v>
       </c>
+      <c r="D13" s="3">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4">
+        <f>D13*C13</f>
+        <v>9.6000000000000013E-6</v>
+      </c>
       <c r="G13" s="7" t="s">
         <v>15</v>
       </c>
@@ -654,11 +662,11 @@
         <v>6.0000000000000008E-7</v>
       </c>
       <c r="D14" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E14" s="4">
         <f>D14*C14</f>
-        <v>1.4400000000000001E-5</v>
+        <v>1.9200000000000003E-5</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>15</v>
@@ -669,18 +677,18 @@
         <v>12</v>
       </c>
       <c r="B15" s="3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C15" s="4">
         <f>1/(B15*10^6)</f>
-        <v>4.9999999999999998E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="D15" s="3">
         <v>100</v>
       </c>
       <c r="E15" s="4">
         <f>D15*C15</f>
-        <v>4.9999999999999996E-6</v>
+        <v>1.9999999999999999E-6</v>
       </c>
       <c r="G15" s="7"/>
     </row>
@@ -705,6 +713,9 @@
       <c r="G16" s="7" t="s">
         <v>16</v>
       </c>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">
